--- a/templates/人员资料导入模板.xlsx
+++ b/templates/人员资料导入模板.xlsx
@@ -411,7 +411,7 @@
     <col min="6" max="6" width="22.83203125" customWidth="1"/>
     <col min="7" max="7" width="26.83203125" customWidth="1"/>
     <col min="8" max="8" width="14.83203125" customWidth="1"/>
-    <col min="9" max="9" width="16.83203125" customWidth="1"/>
+    <col min="9" max="9" width="20.83203125" customWidth="1"/>
     <col min="10" max="10" width="12.83203125" customWidth="1"/>
     <col min="11" max="11" width="16.83203125" customWidth="1"/>
     <col min="12" max="12" width="12.83203125" customWidth="1"/>
@@ -444,7 +444,7 @@
         <v>标准总产能</v>
       </c>
       <c r="I1" t="str">
-        <v>产能释放日期</v>
+        <v>预计产能释放日期</v>
       </c>
       <c r="J1" t="str">
         <v>在岗状态</v>
@@ -549,10 +549,10 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>产能释放日期</v>
+        <v>预计产能释放日期</v>
       </c>
       <c r="B10" t="str">
-        <v>日期未到前，该人员不会进入可调度名单。</v>
+        <v>选填，仅用于排期参考；商务、PM 等持续性岗位或暂无明确日期时可留空。可安排与否按全部有效项目的产能占用合计判断。</v>
       </c>
     </row>
     <row r="11">

--- a/templates/人员资料导入模板.xlsx
+++ b/templates/人员资料导入模板.xlsx
@@ -504,7 +504,7 @@
         <v>职位</v>
       </c>
       <c r="B4" t="str">
-        <v>可填写：AI动画师、导演、UE蓝图动画师、UE场景设计师、AI后期、AI技术研究、CG资产师、商务、导演助理等。</v>
+        <v>支持多选，多项用中文顿号或分号分隔。可填写：总经理、人事总监、项目经理 / PM、AI动画师、导演、UE蓝图动画师、UE场景设计师、AI后期、AI技术研究、CG资产师、商务、导演助理等。</v>
       </c>
     </row>
     <row r="5">

--- a/templates/人员资料导入模板.xlsx
+++ b/templates/人员资料导入模板.xlsx
@@ -528,7 +528,7 @@
         <v>AI项目及产能占用</v>
       </c>
       <c r="B7" t="str">
-        <v>格式：项目名|占用百分比|项目角色|结束日期；多项用中文分号分隔。示例：项目A|60|视频制作人员|2026-08-31。</v>
+        <v>格式：项目名|占用百分比|项目角色|结束日期|资产制作数|资产优化数|视频分钟|高难度镜头分钟|实际产出说明；多项用中文分号分隔。未用到的产出字段可留空。</v>
       </c>
     </row>
     <row r="8">

--- a/templates/人员资料导入模板.xlsx
+++ b/templates/人员资料导入模板.xlsx
@@ -560,7 +560,7 @@
         <v>在岗状态</v>
       </c>
       <c r="B11" t="str">
-        <v>可填写：在岗、请假、异动、停薪留岗、外包、离岗。</v>
+        <v>可填写：在岗、请假、异动、停薪留岗、外包、离职、离岗。只有“在岗”人员进入可调度和项目候选列表。</v>
       </c>
     </row>
     <row r="12">
